--- a/exports/trend_1d/FINNIFTY_full_report.xlsx
+++ b/exports/trend_1d/FINNIFTY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q95"/>
+  <dimension ref="A1:U95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>6.7</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42037</v>
+        <v>42038</v>
       </c>
       <c r="H2" t="n">
-        <v>8025.25</v>
+        <v>7813.5</v>
       </c>
       <c r="I2" t="n">
         <v>7861.486391149059</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>4.26</v>
+        <v>1.51</v>
       </c>
       <c r="L2" t="n">
         <v>1.7</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>8.09</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42063</v>
+        <v>42065</v>
       </c>
       <c r="H3" t="n">
-        <v>8033.45</v>
+        <v>8153.05</v>
       </c>
       <c r="I3" t="n">
         <v>8110.772731395796</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.81</v>
+        <v>-4.35</v>
       </c>
       <c r="L3" t="n">
-        <v>3.27</v>
+        <v>4.87</v>
       </c>
       <c r="M3" t="n">
         <v>0.13</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>6.14</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42076</v>
+        <v>42079</v>
       </c>
       <c r="H4" t="n">
-        <v>7755.7</v>
+        <v>7733.2</v>
       </c>
       <c r="I4" t="n">
         <v>7734.26883160281</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.87</v>
+        <v>-5.15</v>
       </c>
       <c r="L4" t="n">
-        <v>5.02</v>
+        <v>5.66</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0.46</v>
       </c>
       <c r="N4" t="n">
         <v>2.72</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.08</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42143</v>
+        <v>42144</v>
       </c>
       <c r="H5" t="n">
-        <v>7450.7</v>
+        <v>7536.2</v>
       </c>
       <c r="I5" t="n">
         <v>7524.612441935831</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>2.55</v>
       </c>
       <c r="L5" t="n">
         <v>2.93</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>5.92</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42157</v>
+        <v>42158</v>
       </c>
       <c r="H6" t="n">
-        <v>7256.85</v>
+        <v>7175.15</v>
       </c>
       <c r="I6" t="n">
         <v>7199.137155746326</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.71</v>
+        <v>-4.79</v>
       </c>
       <c r="L6" t="n">
-        <v>3.86</v>
+        <v>5.65</v>
       </c>
       <c r="M6" t="n">
         <v>0.28</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>5.67</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42174</v>
+        <v>42177.37402777778</v>
       </c>
       <c r="H7" t="n">
-        <v>7313.4</v>
+        <v>7506.4</v>
       </c>
       <c r="I7" t="n">
         <v>7444.240500088016</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16</v>
+        <v>19.37402777777778</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.93</v>
+        <v>-4.62</v>
       </c>
       <c r="L7" t="n">
-        <v>2.19</v>
+        <v>4.87</v>
       </c>
       <c r="M7" t="n">
         <v>0.61</v>
       </c>
       <c r="N7" t="n">
-        <v>1.48</v>
+        <v>2.64</v>
       </c>
       <c r="O7" t="n">
         <v>-1.13</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>5.97</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42212.34644675926</v>
+        <v>42213.38434027778</v>
       </c>
       <c r="H8" t="n">
-        <v>7537</v>
+        <v>7513.35</v>
       </c>
       <c r="I8" t="n">
         <v>7527.520646803298</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>34.97241898148148</v>
+        <v>36.0103125</v>
       </c>
       <c r="K8" t="n">
-        <v>0.41</v>
+        <v>0.09</v>
       </c>
       <c r="L8" t="n">
         <v>2.47</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>4.86</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42278.34326388889</v>
+        <v>42282.34321759259</v>
       </c>
       <c r="H9" t="n">
-        <v>6996.15</v>
+        <v>7258.25</v>
       </c>
       <c r="I9" t="n">
         <v>7178.765128615869</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>64.95892361111112</v>
+        <v>68.95887731481481</v>
       </c>
       <c r="K9" t="n">
-        <v>6.88</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
         <v>3.78</v>
@@ -954,7 +1061,7 @@
         <v>1.66</v>
       </c>
       <c r="N9" t="n">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
         <v>-0.31</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>8.6</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42312.36326388889</v>
+        <v>42313.35915509259</v>
       </c>
       <c r="H10" t="n">
-        <v>7115.55</v>
+        <v>7025.1</v>
       </c>
       <c r="I10" t="n">
         <v>7103.717898191218</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>30.0200462962963</v>
+        <v>31.0159375</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.97</v>
+        <v>-3.21</v>
       </c>
       <c r="L10" t="n">
-        <v>2.34</v>
+        <v>3.36</v>
       </c>
       <c r="M10" t="n">
         <v>0.93</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>4.98</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42362.38541666666</v>
+        <v>42366.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>6968.3</v>
+        <v>7014.15</v>
       </c>
       <c r="I11" t="n">
         <v>7011.318261605713</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>49.02626157407408</v>
+        <v>53.02626157407408</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="L11" t="n">
         <v>1.81</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,25 +1247,25 @@
         <v>3.83</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42375.38541666666</v>
+        <v>42376.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>6854.25</v>
+        <v>6704</v>
       </c>
       <c r="I12" t="n">
         <v>6830.686652751643</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.28</v>
+        <v>-4.42</v>
       </c>
       <c r="L12" t="n">
-        <v>2.64</v>
+        <v>4.59</v>
       </c>
       <c r="M12" t="n">
-        <v>0.47</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>2.57</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>4.78</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42430.38541666666</v>
+        <v>42431.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>6001.6</v>
+        <v>6247.35</v>
       </c>
       <c r="I13" t="n">
         <v>6075.008808043704</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K13" t="n">
-        <v>10.48</v>
+        <v>6.81</v>
       </c>
       <c r="L13" t="n">
         <v>1.22</v>
       </c>
       <c r="M13" t="n">
-        <v>1.41</v>
+        <v>1.99</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>4.09</v>
       </c>
       <c r="O13" t="n">
         <v>-2.19</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.34</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42639.38541666666</v>
+        <v>42640.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>8100</v>
+        <v>8074</v>
       </c>
       <c r="I14" t="n">
         <v>8091.205171587611</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K14" t="n">
-        <v>29.65</v>
+        <v>29.24</v>
       </c>
       <c r="L14" t="n">
         <v>2.06</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>3.93</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42745.38541666666</v>
+        <v>42746.41388888889</v>
       </c>
       <c r="H15" t="n">
-        <v>7404.4</v>
+        <v>7515.75</v>
       </c>
       <c r="I15" t="n">
         <v>7493.356233929113</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>105</v>
+        <v>106.0284722222222</v>
       </c>
       <c r="K15" t="n">
-        <v>8.289999999999999</v>
+        <v>6.91</v>
       </c>
       <c r="L15" t="n">
         <v>1.42</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>4.11</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42956.38541666666</v>
+        <v>42957.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>10022.25</v>
+        <v>9923.15</v>
       </c>
       <c r="I16" t="n">
         <v>9953.372818183278</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>209.9715277777778</v>
+        <v>210.9715277777778</v>
       </c>
       <c r="K16" t="n">
-        <v>33.35</v>
+        <v>32.03</v>
       </c>
       <c r="L16" t="n">
         <v>1.16</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>3.56</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42989.38541666666</v>
+        <v>42990.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>10185.9</v>
+        <v>10250</v>
       </c>
       <c r="I17" t="n">
         <v>10225.44069334081</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.65</v>
+        <v>-3.29</v>
       </c>
       <c r="L17" t="n">
-        <v>3.01</v>
+        <v>3.36</v>
       </c>
       <c r="M17" t="n">
         <v>0.6</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>3.15</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43000.38541666666</v>
+        <v>43003.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>10064.9</v>
+        <v>9952.75</v>
       </c>
       <c r="I18" t="n">
         <v>10033.60156402747</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.81</v>
+        <v>-2.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>3.47</v>
       </c>
       <c r="M18" t="n">
         <v>0.35</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>3.26</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43035.38541666666</v>
+        <v>43038.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>10178.85</v>
+        <v>10222.4</v>
       </c>
       <c r="I19" t="n">
         <v>10206.81835985221</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.27</v>
+        <v>-2.71</v>
       </c>
       <c r="L19" t="n">
         <v>3.24</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>3.41</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43069.38541666666</v>
+        <v>43070.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>10324.85</v>
+        <v>10256.15</v>
       </c>
       <c r="I20" t="n">
         <v>10285.69269903669</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="L20" t="n">
         <v>0.45</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>3.43</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43087.38541666666</v>
+        <v>43088.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>10477.75</v>
+        <v>10522.25</v>
       </c>
       <c r="I21" t="n">
         <v>10483.46596552562</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.16</v>
+        <v>-2.59</v>
       </c>
       <c r="L21" t="n">
         <v>2.76</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>4.08</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43132.38541666666</v>
+        <v>43133.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>11231.75</v>
+        <v>10886.9</v>
       </c>
       <c r="I22" t="n">
         <v>10927.82376635567</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K22" t="n">
-        <v>6.74</v>
+        <v>3.47</v>
       </c>
       <c r="L22" t="n">
         <v>1.63</v>
       </c>
       <c r="M22" t="n">
-        <v>0.51</v>
+        <v>0.78</v>
       </c>
       <c r="N22" t="n">
-        <v>1.09</v>
+        <v>3.07</v>
       </c>
       <c r="O22" t="n">
         <v>0.42</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.42</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43195.38541666666</v>
+        <v>43196.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>10414.55</v>
+        <v>10468.15</v>
       </c>
       <c r="I23" t="n">
         <v>10416.95455492159</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K23" t="n">
-        <v>4.34</v>
+        <v>3.85</v>
       </c>
       <c r="L23" t="n">
         <v>2.38</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.62</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43238.38541666666</v>
+        <v>43241.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>10783.2</v>
+        <v>10693.65</v>
       </c>
       <c r="I24" t="n">
         <v>10752.60707367731</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K24" t="n">
-        <v>3.01</v>
+        <v>2.15</v>
       </c>
       <c r="L24" t="n">
         <v>1.14</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>3.8</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43250.38541666666</v>
+        <v>43251.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>10899.45</v>
+        <v>11131.7</v>
       </c>
       <c r="I25" t="n">
         <v>11030.22046213286</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.92</v>
+        <v>-4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>3.29</v>
+        <v>4.65</v>
       </c>
       <c r="M25" t="n">
-        <v>0.44</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>1.2</v>
+        <v>2.13</v>
       </c>
       <c r="O25" t="n">
         <v>-0.83</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.49</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43347.38541666666</v>
+        <v>43348.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>11521.6</v>
+        <v>11459.65</v>
       </c>
       <c r="I26" t="n">
         <v>11478.960668291</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K26" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="L26" t="n">
         <v>3.02</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>3.32</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43417.38541666666</v>
+        <v>43418.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>10867.6</v>
+        <v>10934.95</v>
       </c>
       <c r="I27" t="n">
         <v>10879.37832662799</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K27" t="n">
-        <v>5.17</v>
+        <v>4.58</v>
       </c>
       <c r="L27" t="n">
         <v>0.82</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.91</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H28" t="n">
-        <v>11483.6</v>
+        <v>11266.5</v>
       </c>
       <c r="I28" t="n">
         <v>11328.64595019421</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>71.61458333333333</v>
+        <v>74.61458333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>5.02</v>
+        <v>3.03</v>
       </c>
       <c r="L28" t="n">
         <v>0.89</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>4.33</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43529</v>
+        <v>43530</v>
       </c>
       <c r="H29" t="n">
-        <v>11500.55</v>
+        <v>11581.2</v>
       </c>
       <c r="I29" t="n">
         <v>11580.67409888283</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.08</v>
+        <v>-2.79</v>
       </c>
       <c r="L29" t="n">
         <v>3.72</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>3.72</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H30" t="n">
-        <v>12363.65</v>
+        <v>12216.15</v>
       </c>
       <c r="I30" t="n">
         <v>12220.56645174205</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K30" t="n">
-        <v>6.76</v>
+        <v>5.48</v>
       </c>
       <c r="L30" t="n">
         <v>0.62</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>4.51</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H31" t="n">
-        <v>12640.8</v>
+        <v>13222.45</v>
       </c>
       <c r="I31" t="n">
         <v>12662.24933748221</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.48</v>
+        <v>-8.24</v>
       </c>
       <c r="L31" t="n">
-        <v>3.77</v>
+        <v>8.57</v>
       </c>
       <c r="M31" t="n">
-        <v>0.46</v>
+        <v>2.47</v>
       </c>
       <c r="N31" t="n">
-        <v>2.56</v>
+        <v>4.6</v>
       </c>
       <c r="O31" t="n">
         <v>-1.19</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.12</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43655</v>
+        <v>43656</v>
       </c>
       <c r="H32" t="n">
-        <v>13368.8</v>
+        <v>13314.35</v>
       </c>
       <c r="I32" t="n">
         <v>13362.04756431185</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K32" t="n">
-        <v>1.11</v>
+        <v>0.7</v>
       </c>
       <c r="L32" t="n">
         <v>2.29</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>4.41</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H33" t="n">
-        <v>12001.25</v>
+        <v>12859.85</v>
       </c>
       <c r="I33" t="n">
         <v>12635.15887170813</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K33" t="n">
-        <v>9.859999999999999</v>
+        <v>3.41</v>
       </c>
       <c r="L33" t="n">
         <v>1.91</v>
@@ -2322,7 +2717,7 @@
         <v>2.39</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>7.15</v>
       </c>
       <c r="O33" t="n">
         <v>-0.41</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.42</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43833</v>
+        <v>43836</v>
       </c>
       <c r="H34" t="n">
-        <v>14560.7</v>
+        <v>14202.5</v>
       </c>
       <c r="I34" t="n">
         <v>14280.55413588453</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K34" t="n">
-        <v>13.23</v>
+        <v>10.44</v>
       </c>
       <c r="L34" t="n">
         <v>6.77</v>
@@ -2379,7 +2786,7 @@
         <v>0.66</v>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="O34" t="n">
         <v>7.15</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>4.2</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43866</v>
+        <v>43867</v>
       </c>
       <c r="H35" t="n">
-        <v>14407.8</v>
+        <v>14545.75</v>
       </c>
       <c r="I35" t="n">
         <v>14421.83821480661</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.45</v>
+        <v>-2.42</v>
       </c>
       <c r="L35" t="n">
         <v>3.51</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>5.33</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H36" t="n">
-        <v>14086.05</v>
+        <v>13566.45</v>
       </c>
       <c r="I36" t="n">
         <v>14079.00101542147</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.16</v>
+        <v>-6.73</v>
       </c>
       <c r="L36" t="n">
-        <v>4.07</v>
+        <v>7.05</v>
       </c>
       <c r="M36" t="n">
-        <v>0.77</v>
+        <v>2.18</v>
       </c>
       <c r="N36" t="n">
-        <v>1.89</v>
+        <v>3.69</v>
       </c>
       <c r="O36" t="n">
         <v>0.96</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.69</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H37" t="n">
-        <v>9873.5</v>
+        <v>10187.95</v>
       </c>
       <c r="I37" t="n">
         <v>9904.897180609712</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K37" t="n">
-        <v>27.22</v>
+        <v>24.9</v>
       </c>
       <c r="L37" t="n">
         <v>2.28</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.02</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44043</v>
+        <v>44046</v>
       </c>
       <c r="H38" t="n">
-        <v>10728.85</v>
+        <v>10467.2</v>
       </c>
       <c r="I38" t="n">
         <v>10541.48715825737</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K38" t="n">
-        <v>5.31</v>
+        <v>2.74</v>
       </c>
       <c r="L38" t="n">
         <v>5.91</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>8.56</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44068</v>
+        <v>44069</v>
       </c>
       <c r="H39" t="n">
-        <v>11358.95</v>
+        <v>11416.7</v>
       </c>
       <c r="I39" t="n">
         <v>11362.86912505819</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>-8.52</v>
+        <v>-9.07</v>
       </c>
       <c r="L39" t="n">
-        <v>8.74</v>
+        <v>9.24</v>
       </c>
       <c r="M39" t="n">
         <v>0.99</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>5.39</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44082</v>
+        <v>44083</v>
       </c>
       <c r="H40" t="n">
-        <v>11086.2</v>
+        <v>10887.6</v>
       </c>
       <c r="I40" t="n">
         <v>11030.7574007304</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.89</v>
+        <v>-4.63</v>
       </c>
       <c r="L40" t="n">
-        <v>3.24</v>
+        <v>5.16</v>
       </c>
       <c r="M40" t="n">
         <v>1.65</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.72</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44104</v>
+        <v>44105</v>
       </c>
       <c r="H41" t="n">
-        <v>10622.4</v>
+        <v>10949.6</v>
       </c>
       <c r="I41" t="n">
         <v>10923.23786794961</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K41" t="n">
-        <v>2.44</v>
+        <v>-0.57</v>
       </c>
       <c r="L41" t="n">
         <v>1.82</v>
@@ -2778,7 +3269,7 @@
         <v>1.21</v>
       </c>
       <c r="N41" t="n">
-        <v>2.51</v>
+        <v>3.08</v>
       </c>
       <c r="O41" t="n">
         <v>-1.79</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.64</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H42" t="n">
-        <v>15143.65</v>
+        <v>14723.9</v>
       </c>
       <c r="I42" t="n">
         <v>14994.3948142714</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K42" t="n">
-        <v>38.3</v>
+        <v>34.47</v>
       </c>
       <c r="L42" t="n">
         <v>2.12</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>7.26</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44225</v>
+        <v>44228</v>
       </c>
       <c r="H43" t="n">
-        <v>14593.3</v>
+        <v>15702.45</v>
       </c>
       <c r="I43" t="n">
         <v>15388.37160722334</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>0.89</v>
+        <v>-6.65</v>
       </c>
       <c r="L43" t="n">
-        <v>2.94</v>
+        <v>7.11</v>
       </c>
       <c r="M43" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O43" t="n">
         <v>-2.77</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>10.31</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44252</v>
+        <v>44253</v>
       </c>
       <c r="H44" t="n">
-        <v>16919.3</v>
+        <v>16085.25</v>
       </c>
       <c r="I44" t="n">
         <v>16387.5688530638</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K44" t="n">
-        <v>7.75</v>
+        <v>2.44</v>
       </c>
       <c r="L44" t="n">
         <v>6.18</v>
       </c>
       <c r="M44" t="n">
-        <v>0.59</v>
+        <v>1.78</v>
       </c>
       <c r="N44" t="n">
-        <v>1.6</v>
+        <v>4.93</v>
       </c>
       <c r="O44" t="n">
         <v>7.6</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.57</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44314</v>
+        <v>44315</v>
       </c>
       <c r="H45" t="n">
-        <v>16039.75</v>
+        <v>16047.05</v>
       </c>
       <c r="I45" t="n">
         <v>16042.40972776647</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K45" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="L45" t="n">
         <v>5.46</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.18</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
       <c r="H46" t="n">
-        <v>16555.75</v>
+        <v>16293.1</v>
       </c>
       <c r="I46" t="n">
         <v>16349.45039829842</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K46" t="n">
-        <v>3.17</v>
+        <v>1.53</v>
       </c>
       <c r="L46" t="n">
         <v>5.04</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>4.43</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44411</v>
+        <v>44412</v>
       </c>
       <c r="H47" t="n">
-        <v>16818.05</v>
+        <v>17253.05</v>
       </c>
       <c r="I47" t="n">
         <v>17014.46892737828</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.22</v>
+        <v>-5.89</v>
       </c>
       <c r="L47" t="n">
-        <v>3.32</v>
+        <v>6.25</v>
       </c>
       <c r="M47" t="n">
         <v>0.71</v>
       </c>
       <c r="N47" t="n">
-        <v>1.68</v>
+        <v>2.59</v>
       </c>
       <c r="O47" t="n">
         <v>-1.59</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.07</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44516</v>
+        <v>44517</v>
       </c>
       <c r="H48" t="n">
-        <v>18805.75</v>
+        <v>18679.95</v>
       </c>
       <c r="I48" t="n">
         <v>18760.97897040025</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K48" t="n">
-        <v>9</v>
+        <v>8.27</v>
       </c>
       <c r="L48" t="n">
         <v>2.23</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>4.66</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44564</v>
+        <v>44565</v>
       </c>
       <c r="H49" t="n">
-        <v>17761.05</v>
+        <v>17972.95</v>
       </c>
       <c r="I49" t="n">
         <v>17930.5504521339</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K49" t="n">
-        <v>4.92</v>
+        <v>3.78</v>
       </c>
       <c r="L49" t="n">
         <v>1</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>5.68</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H50" t="n">
-        <v>18047.05</v>
+        <v>17633.45</v>
       </c>
       <c r="I50" t="n">
         <v>17813.57346348704</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>0.41</v>
+        <v>-1.89</v>
       </c>
       <c r="L50" t="n">
-        <v>1.37</v>
+        <v>3.25</v>
       </c>
       <c r="M50" t="n">
         <v>1.23</v>
       </c>
       <c r="N50" t="n">
-        <v>1.08</v>
+        <v>2.29</v>
       </c>
       <c r="O50" t="n">
         <v>1.19</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.82</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H51" t="n">
-        <v>16675.5</v>
+        <v>17137.4</v>
       </c>
       <c r="I51" t="n">
         <v>16783.72458126241</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K51" t="n">
-        <v>5.43</v>
+        <v>2.81</v>
       </c>
       <c r="L51" t="n">
         <v>4.52</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.74</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44669</v>
+        <v>44670</v>
       </c>
       <c r="H52" t="n">
-        <v>17034.65</v>
+        <v>16708.9</v>
       </c>
       <c r="I52" t="n">
         <v>16865.07185897482</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.6</v>
+        <v>-2.5</v>
       </c>
       <c r="L52" t="n">
         <v>4.45</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.52</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44708</v>
+        <v>44711</v>
       </c>
       <c r="H53" t="n">
-        <v>16476.05</v>
+        <v>16629.2</v>
       </c>
       <c r="I53" t="n">
         <v>16508.44924471141</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K53" t="n">
-        <v>1.39</v>
+        <v>0.48</v>
       </c>
       <c r="L53" t="n">
         <v>2.35</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>5.63</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44722</v>
+        <v>44725</v>
       </c>
       <c r="H54" t="n">
-        <v>15847.3</v>
+        <v>15356.4</v>
       </c>
       <c r="I54" t="n">
         <v>15693.04154397969</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.7</v>
+        <v>-7.65</v>
       </c>
       <c r="L54" t="n">
-        <v>4.93</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>1.13</v>
+        <v>2.3</v>
       </c>
       <c r="N54" t="n">
-        <v>2.24</v>
+        <v>3.1</v>
       </c>
       <c r="O54" t="n">
         <v>0.93</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>6.33</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44747</v>
+        <v>44748</v>
       </c>
       <c r="H55" t="n">
-        <v>15729.15</v>
+        <v>15980.25</v>
       </c>
       <c r="I55" t="n">
         <v>15929.21378230207</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.43</v>
+        <v>-4.06</v>
       </c>
       <c r="L55" t="n">
-        <v>4.07</v>
+        <v>4.26</v>
       </c>
       <c r="M55" t="n">
         <v>1.48</v>
       </c>
       <c r="N55" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="O55" t="n">
         <v>-3.1</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>5.76</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44799</v>
+        <v>44802</v>
       </c>
       <c r="H56" t="n">
-        <v>17933.9</v>
+        <v>17631.7</v>
       </c>
       <c r="I56" t="n">
         <v>17695.39776736448</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K56" t="n">
-        <v>12.23</v>
+        <v>10.33</v>
       </c>
       <c r="L56" t="n">
         <v>1.53</v>
       </c>
       <c r="M56" t="n">
-        <v>0.77</v>
+        <v>2.23</v>
       </c>
       <c r="N56" t="n">
         <v>1.94</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>4.4</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44811</v>
+        <v>44812</v>
       </c>
       <c r="H57" t="n">
-        <v>18140.5</v>
+        <v>18409.45</v>
       </c>
       <c r="I57" t="n">
         <v>18407.04841248765</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.89</v>
+        <v>-4.41</v>
       </c>
       <c r="L57" t="n">
-        <v>4.28</v>
+        <v>4.51</v>
       </c>
       <c r="M57" t="n">
-        <v>0.58</v>
+        <v>0.74</v>
       </c>
       <c r="N57" t="n">
         <v>3.42</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>4.8</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H58" t="n">
-        <v>17947.25</v>
+        <v>17565.3</v>
       </c>
       <c r="I58" t="n">
         <v>17933.64387688986</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.51</v>
+        <v>-4.59</v>
       </c>
       <c r="L58" t="n">
-        <v>2.86</v>
+        <v>4.88</v>
       </c>
       <c r="M58" t="n">
         <v>1.46</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>6.27</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44855</v>
+        <v>44858</v>
       </c>
       <c r="H59" t="n">
-        <v>18194.1</v>
+        <v>18424.75</v>
       </c>
       <c r="I59" t="n">
         <v>18247.92985683605</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.58</v>
+        <v>-4.89</v>
       </c>
       <c r="L59" t="n">
-        <v>4.19</v>
+        <v>5.19</v>
       </c>
       <c r="M59" t="n">
         <v>1.94</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>4.49</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="H60" t="n">
-        <v>19222.3</v>
+        <v>18925.2</v>
       </c>
       <c r="I60" t="n">
         <v>18981.17437510218</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K60" t="n">
-        <v>4.33</v>
+        <v>2.72</v>
       </c>
       <c r="L60" t="n">
         <v>1.12</v>
@@ -3861,7 +4580,7 @@
         <v>0.74</v>
       </c>
       <c r="N60" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="O60" t="n">
         <v>1.27</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>4.24</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45019</v>
+        <v>45021</v>
       </c>
       <c r="H61" t="n">
-        <v>18164.75</v>
+        <v>18372.15</v>
       </c>
       <c r="I61" t="n">
         <v>18259.25317848084</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K61" t="n">
-        <v>4.02</v>
+        <v>2.92</v>
       </c>
       <c r="L61" t="n">
         <v>2.13</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>5</v>
+      </c>
+      <c r="U61" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>4.18</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45140</v>
+        <v>45141</v>
       </c>
       <c r="H62" t="n">
-        <v>20066.95</v>
+        <v>19832.45</v>
       </c>
       <c r="I62" t="n">
         <v>19946.09339178383</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K62" t="n">
-        <v>9.220000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="L62" t="n">
         <v>0.95</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>3.88</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45176</v>
+        <v>45177</v>
       </c>
       <c r="H63" t="n">
-        <v>19960.7</v>
+        <v>20138.1</v>
       </c>
       <c r="I63" t="n">
         <v>20055.392374585</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.65</v>
+        <v>-1.54</v>
       </c>
       <c r="L63" t="n">
-        <v>1.45</v>
+        <v>1.96</v>
       </c>
       <c r="M63" t="n">
         <v>0.52</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>3.15</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45189</v>
+        <v>45190</v>
       </c>
       <c r="H64" t="n">
-        <v>20104.5</v>
+        <v>19814.95</v>
       </c>
       <c r="I64" t="n">
         <v>19939.0362921171</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.17</v>
+        <v>-1.6</v>
       </c>
       <c r="L64" t="n">
-        <v>0.92</v>
+        <v>1.68</v>
       </c>
       <c r="M64" t="n">
         <v>1.06</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,25 +4904,25 @@
         <v>3.73</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45243</v>
+        <v>45245</v>
       </c>
       <c r="H65" t="n">
-        <v>19542.15</v>
+        <v>19722.85</v>
       </c>
       <c r="I65" t="n">
         <v>19690.69506531357</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K65" t="n">
-        <v>1.38</v>
+        <v>0.46</v>
       </c>
       <c r="L65" t="n">
         <v>1.1</v>
       </c>
       <c r="M65" t="n">
-        <v>0.84</v>
+        <v>1.11</v>
       </c>
       <c r="N65" t="n">
         <v>1.23</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>2.85</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45307</v>
+        <v>45308</v>
       </c>
       <c r="H66" t="n">
-        <v>21447.15</v>
+        <v>20528.9</v>
       </c>
       <c r="I66" t="n">
         <v>20884.58091121422</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K66" t="n">
-        <v>8.74</v>
+        <v>4.09</v>
       </c>
       <c r="L66" t="n">
         <v>1.3</v>
       </c>
       <c r="M66" t="n">
-        <v>1.19</v>
+        <v>3.33</v>
       </c>
       <c r="N66" t="n">
-        <v>1.09</v>
+        <v>4.28</v>
       </c>
       <c r="O66" t="n">
         <v>0.92</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>5.14</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45356</v>
+        <v>45357</v>
       </c>
       <c r="H67" t="n">
-        <v>20854.5</v>
+        <v>20986.15</v>
       </c>
       <c r="I67" t="n">
         <v>20976.92225475574</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.59</v>
+        <v>-2.23</v>
       </c>
       <c r="L67" t="n">
-        <v>2.37</v>
+        <v>2.61</v>
       </c>
       <c r="M67" t="n">
         <v>0.9399999999999999</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>3.65</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45397</v>
+        <v>45398</v>
       </c>
       <c r="H68" t="n">
-        <v>21146</v>
+        <v>21099.25</v>
       </c>
       <c r="I68" t="n">
         <v>21112.86561922096</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K68" t="n">
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
       <c r="L68" t="n">
         <v>2.97</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>2.89</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45408</v>
+        <v>45411</v>
       </c>
       <c r="H69" t="n">
-        <v>21354.05</v>
+        <v>21811.2</v>
       </c>
       <c r="I69" t="n">
         <v>21709.10578858792</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.21</v>
+        <v>-3.37</v>
       </c>
       <c r="L69" t="n">
-        <v>2.43</v>
+        <v>3.47</v>
       </c>
       <c r="M69" t="n">
         <v>1.12</v>
       </c>
       <c r="N69" t="n">
-        <v>1.31</v>
+        <v>2.14</v>
       </c>
       <c r="O69" t="n">
         <v>-0.22</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>4.61</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H70" t="n">
-        <v>21428.35</v>
+        <v>21093.5</v>
       </c>
       <c r="I70" t="n">
         <v>21101.16329866666</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.76</v>
+        <v>-3.29</v>
       </c>
       <c r="L70" t="n">
-        <v>1.9</v>
+        <v>3.39</v>
       </c>
       <c r="M70" t="n">
         <v>0.4</v>
       </c>
       <c r="N70" t="n">
-        <v>0.92</v>
+        <v>1.56</v>
       </c>
       <c r="O70" t="n">
         <v>2.14</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>4.79</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c r="H71" t="n">
-        <v>21852.3</v>
+        <v>21965.6</v>
       </c>
       <c r="I71" t="n">
         <v>21958.84764375156</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K71" t="n">
-        <v>-3.6</v>
+        <v>-4.13</v>
       </c>
       <c r="L71" t="n">
-        <v>3.78</v>
+        <v>4.98</v>
       </c>
       <c r="M71" t="n">
         <v>0.58</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>3.26</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H72" t="n">
-        <v>22596.4</v>
+        <v>20819.5</v>
       </c>
       <c r="I72" t="n">
         <v>21506.62333918343</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K72" t="n">
-        <v>2.87</v>
+        <v>-5.22</v>
       </c>
       <c r="L72" t="n">
-        <v>1.98</v>
+        <v>6.86</v>
       </c>
       <c r="M72" t="n">
         <v>0.7</v>
       </c>
       <c r="N72" t="n">
-        <v>1.65</v>
+        <v>7.86</v>
       </c>
       <c r="O72" t="n">
         <v>0.52</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>10.31</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45461</v>
+        <v>45462</v>
       </c>
       <c r="H73" t="n">
-        <v>22585.35</v>
+        <v>22943.95</v>
       </c>
       <c r="I73" t="n">
         <v>22911.03734526142</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K73" t="n">
-        <v>-8.48</v>
+        <v>-10.2</v>
       </c>
       <c r="L73" t="n">
-        <v>8.710000000000001</v>
+        <v>11.21</v>
       </c>
       <c r="M73" t="n">
         <v>1.1</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>5.57</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H74" t="n">
-        <v>23365.9</v>
+        <v>22762.7</v>
       </c>
       <c r="I74" t="n">
         <v>22875.48523893669</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K74" t="n">
-        <v>1.84</v>
+        <v>-0.79</v>
       </c>
       <c r="L74" t="n">
         <v>1.56</v>
       </c>
       <c r="M74" t="n">
-        <v>1.05</v>
+        <v>1.63</v>
       </c>
       <c r="N74" t="n">
-        <v>1.37</v>
+        <v>2.58</v>
       </c>
       <c r="O74" t="n">
         <v>1.59</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>4.91</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45533</v>
+        <v>45534</v>
       </c>
       <c r="H75" t="n">
-        <v>23581.7</v>
+        <v>23637.9</v>
       </c>
       <c r="I75" t="n">
         <v>23601.28541820194</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K75" t="n">
-        <v>-3.6</v>
+        <v>-3.84</v>
       </c>
       <c r="L75" t="n">
-        <v>4.01</v>
+        <v>4.2</v>
       </c>
       <c r="M75" t="n">
         <v>1.17</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>2.95</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H76" t="n">
-        <v>24477.45</v>
+        <v>23881.55</v>
       </c>
       <c r="I76" t="n">
         <v>24322.06218835019</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K76" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="L76" t="n">
         <v>0.83</v>
       </c>
       <c r="M76" t="n">
-        <v>0.63</v>
+        <v>1.07</v>
       </c>
       <c r="N76" t="n">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="O76" t="n">
         <v>0.24</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>4.63</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="H77" t="n">
-        <v>24072.65</v>
+        <v>24296.55</v>
       </c>
       <c r="I77" t="n">
         <v>24289.59179122304</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.8</v>
+        <v>-1.74</v>
       </c>
       <c r="L77" t="n">
         <v>2.09</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,25 +5801,25 @@
         <v>4.24</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="H78" t="n">
-        <v>24198.35</v>
+        <v>23906.6</v>
       </c>
       <c r="I78" t="n">
         <v>23931.85536083437</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.4</v>
+        <v>-1.6</v>
       </c>
       <c r="L78" t="n">
-        <v>0.65</v>
+        <v>2.07</v>
       </c>
       <c r="M78" t="n">
-        <v>0.34</v>
+        <v>1.34</v>
       </c>
       <c r="N78" t="n">
         <v>1.44</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>4.03</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45691</v>
+        <v>45692</v>
       </c>
       <c r="H79" t="n">
-        <v>23132.45</v>
+        <v>23620.7</v>
       </c>
       <c r="I79" t="n">
         <v>23374.27308083092</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K79" t="n">
-        <v>3.24</v>
+        <v>1.2</v>
       </c>
       <c r="L79" t="n">
         <v>0.59</v>
@@ -4944,7 +5891,7 @@
         <v>1.2</v>
       </c>
       <c r="N79" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="O79" t="n">
         <v>-1.21</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>3</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>5.23</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H80" t="n">
-        <v>24774.3</v>
+        <v>23908.45</v>
       </c>
       <c r="I80" t="n">
         <v>24263.88528707939</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K80" t="n">
-        <v>4.88</v>
+        <v>1.22</v>
       </c>
       <c r="L80" t="n">
         <v>3.39</v>
       </c>
       <c r="M80" t="n">
-        <v>0.87</v>
+        <v>4.06</v>
       </c>
       <c r="N80" t="n">
-        <v>2.18</v>
+        <v>3.49</v>
       </c>
       <c r="O80" t="n">
         <v>2.11</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>3</v>
+      </c>
+      <c r="U80" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -5037,28 +6008,28 @@
         <v>4.86</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H81" t="n">
-        <v>24555.55</v>
+        <v>25280.65</v>
       </c>
       <c r="I81" t="n">
         <v>25070.41368366788</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K81" t="n">
-        <v>-2.71</v>
+        <v>-5.74</v>
       </c>
       <c r="L81" t="n">
-        <v>3.3</v>
+        <v>5.96</v>
       </c>
       <c r="M81" t="n">
-        <v>0.98</v>
+        <v>2.69</v>
       </c>
       <c r="N81" t="n">
-        <v>1.75</v>
+        <v>2.95</v>
       </c>
       <c r="O81" t="n">
         <v>-3.49</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S81" t="b">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>5.72</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>45873</v>
+        <v>45874</v>
       </c>
       <c r="H82" t="n">
-        <v>26476.6</v>
+        <v>26373.5</v>
       </c>
       <c r="I82" t="n">
         <v>26408.36502711408</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K82" t="n">
-        <v>4.73</v>
+        <v>4.32</v>
       </c>
       <c r="L82" t="n">
         <v>0.97</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>5</v>
+      </c>
+      <c r="U82" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -5151,19 +6146,19 @@
         <v>2.8</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="H83" t="n">
-        <v>26363.25</v>
+        <v>26393.05</v>
       </c>
       <c r="I83" t="n">
         <v>26380.72830680739</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K83" t="n">
-        <v>0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L83" t="n">
         <v>1.77</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,28 +6215,28 @@
         <v>2.49</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H84" t="n">
-        <v>26247.4</v>
+        <v>25985.25</v>
       </c>
       <c r="I84" t="n">
         <v>26043.02315803907</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.55</v>
+        <v>-1.55</v>
       </c>
       <c r="L84" t="n">
-        <v>0.65</v>
+        <v>1.7</v>
       </c>
       <c r="M84" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="N84" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
         <v>0.11</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5265,25 +6284,25 @@
         <v>2.83</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="H85" t="n">
-        <v>26426.75</v>
+        <v>26712.05</v>
       </c>
       <c r="I85" t="n">
         <v>26651.4941138042</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K85" t="n">
-        <v>-1.7</v>
+        <v>-2.8</v>
       </c>
       <c r="L85" t="n">
-        <v>1.75</v>
+        <v>2.84</v>
       </c>
       <c r="M85" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="N85" t="n">
         <v>1.38</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,19 +6353,19 @@
         <v>3.03</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H86" t="n">
-        <v>27518.95</v>
+        <v>27200.6</v>
       </c>
       <c r="I86" t="n">
         <v>27270.55131468041</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K86" t="n">
-        <v>3.02</v>
+        <v>1.83</v>
       </c>
       <c r="L86" t="n">
         <v>0.83</v>
@@ -5343,7 +6374,7 @@
         <v>0.71</v>
       </c>
       <c r="N86" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="O86" t="n">
         <v>1.08</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>4</v>
+      </c>
+      <c r="U86" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -5379,19 +6422,19 @@
         <v>3.22</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H87" t="n">
-        <v>27674.05</v>
+        <v>27802.55</v>
       </c>
       <c r="I87" t="n">
         <v>27790.7363220509</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K87" t="n">
-        <v>-1.74</v>
+        <v>-2.21</v>
       </c>
       <c r="L87" t="n">
         <v>3.95</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5436,28 +6491,28 @@
         <v>5.36</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H88" t="n">
-        <v>27564.1</v>
+        <v>27020.45</v>
       </c>
       <c r="I88" t="n">
         <v>27423.19009823232</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.86</v>
+        <v>-2.81</v>
       </c>
       <c r="L88" t="n">
-        <v>1.81</v>
+        <v>3.36</v>
       </c>
       <c r="M88" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="N88" t="n">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="O88" t="n">
         <v>0.46</v>
@@ -5466,7 +6521,19 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>2</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -5493,28 +6560,28 @@
         <v>4.33</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H89" t="n">
-        <v>24685.55</v>
+        <v>26053.05</v>
       </c>
       <c r="I89" t="n">
         <v>25697.18704316189</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K89" t="n">
-        <v>8.640000000000001</v>
+        <v>3.58</v>
       </c>
       <c r="L89" t="n">
         <v>1.17</v>
       </c>
       <c r="M89" t="n">
-        <v>2.58</v>
+        <v>4.06</v>
       </c>
       <c r="N89" t="n">
-        <v>2.35</v>
+        <v>5.54</v>
       </c>
       <c r="O89" t="n">
         <v>-1.97</v>
@@ -5523,7 +6590,19 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>2</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -5550,28 +6629,28 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H90" t="n">
-        <v>25655.45</v>
+        <v>25137.15</v>
       </c>
       <c r="I90" t="n">
         <v>25191.9813684661</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K90" t="n">
-        <v>-1.53</v>
+        <v>-3.52</v>
       </c>
       <c r="L90" t="n">
-        <v>2.16</v>
+        <v>3.67</v>
       </c>
       <c r="M90" t="n">
         <v>2.17</v>
       </c>
       <c r="N90" t="n">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="O90" t="n">
         <v>5.54</v>
@@ -5580,7 +6659,19 @@
         <v>1</v>
       </c>
       <c r="Q90" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S90" t="b">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>2</v>
+      </c>
+      <c r="U90" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -5607,25 +6698,25 @@
         <v>6.15</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="H91" t="n">
-        <v>25943.35</v>
+        <v>26274.8</v>
       </c>
       <c r="I91" t="n">
         <v>26043.19360608788</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K91" t="n">
-        <v>-3.21</v>
+        <v>-4.53</v>
       </c>
       <c r="L91" t="n">
-        <v>4.15</v>
+        <v>5.47</v>
       </c>
       <c r="M91" t="n">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="N91" t="n">
         <v>3.15</v>
@@ -5637,7 +6728,19 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S91" t="b">
+        <v>1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>2</v>
+      </c>
+      <c r="U91" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -5664,22 +6767,22 @@
         <v>4.73</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="H92" t="n">
-        <v>26188.85</v>
+        <v>25992.05</v>
       </c>
       <c r="I92" t="n">
         <v>26137.79518531143</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.33</v>
+        <v>-1.08</v>
       </c>
       <c r="L92" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="M92" t="n">
         <v>1.29</v>
@@ -5694,7 +6797,19 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S92" t="b">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
+        <v>2</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -5721,28 +6836,28 @@
         <v>4.14</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="H93" t="n">
-        <v>26594.05</v>
+        <v>26984.45</v>
       </c>
       <c r="I93" t="n">
         <v>26864.58589412602</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K93" t="n">
-        <v>-2.32</v>
+        <v>-3.82</v>
       </c>
       <c r="L93" t="n">
-        <v>2.42</v>
+        <v>3.82</v>
       </c>
       <c r="M93" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="N93" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="O93" t="n">
         <v>-0.75</v>
@@ -5751,7 +6866,19 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S93" t="b">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>2</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -5778,25 +6905,25 @@
         <v>4.05</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="H94" t="n">
-        <v>26003.9</v>
+        <v>25813.05</v>
       </c>
       <c r="I94" t="n">
         <v>25963.26728318989</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K94" t="n">
-        <v>-3.63</v>
+        <v>-4.34</v>
       </c>
       <c r="L94" t="n">
-        <v>4.03</v>
+        <v>4.87</v>
       </c>
       <c r="M94" t="n">
-        <v>0.6</v>
+        <v>0.87</v>
       </c>
       <c r="N94" t="n">
         <v>1.48</v>
@@ -5808,7 +6935,19 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R94" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S94" t="b">
+        <v>1</v>
+      </c>
+      <c r="T94" t="n">
+        <v>2</v>
+      </c>
+      <c r="U94" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -5859,6 +6998,14 @@
       <c r="Q95" t="n">
         <v>38</v>
       </c>
+      <c r="R95" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S95" t="b">
+        <v>1</v>
+      </c>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10817,7 +11964,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="6">
@@ -10827,7 +11974,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -10837,7 +11984,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8">
@@ -10847,7 +11994,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -10857,7 +12004,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -10867,7 +12014,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101.6</v>
+        <v>103.4</v>
       </c>
     </row>
     <row r="11">
@@ -10877,7 +12024,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -10887,7 +12034,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -10897,7 +12044,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>41.9</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="14">
@@ -10907,7 +12054,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.44</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
@@ -10917,7 +12064,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.05</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="16">
@@ -10927,7 +12074,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.79</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="17">
@@ -10937,7 +12084,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38.3</v>
+        <v>34.47</v>
       </c>
     </row>
     <row r="18">
@@ -10947,7 +12094,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.7</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="19">
@@ -10957,7 +12104,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.68</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="20">
@@ -10967,7 +12114,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.34</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="21">
@@ -10977,7 +12124,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.74</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="22">
@@ -10987,7 +12134,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -10997,7 +12144,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -11007,7 +12154,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="25">
@@ -11027,7 +12174,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.15</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="27">
@@ -11047,7 +12194,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
